--- a/data/trans_orig/P16A13-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A13-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13238</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30264</t>
+          <t>31585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>19295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40189</t>
+          <t>39022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>677035</t>
+          <t>678147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>689070</t>
+          <t>689072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>658087</t>
+          <t>656766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>675113</t>
+          <t>675270</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1341156</t>
+          <t>1342323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1362180</t>
+          <t>1362050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21362</t>
+          <t>20576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>43017</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>20278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42026</t>
+          <t>41874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47203</t>
+          <t>45949</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77673</t>
+          <t>77715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>917811</t>
+          <t>918783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>940438</t>
+          <t>941224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>926367</t>
+          <t>926519</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>948555</t>
+          <t>948115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1852520</t>
+          <t>1852478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1882990</t>
+          <t>1884244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>15850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36593</t>
+          <t>35952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>22412</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43488</t>
+          <t>43229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43416</t>
+          <t>42969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71890</t>
+          <t>71666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641916</t>
+          <t>642557</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661738</t>
+          <t>662659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>640353</t>
+          <t>640612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>661930</t>
+          <t>661429</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1290460</t>
+          <t>1290684</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1318934</t>
+          <t>1319381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14777</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34287</t>
+          <t>34599</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29355</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54907</t>
+          <t>53767</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47880</t>
+          <t>48964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79214</t>
+          <t>79698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>907935</t>
+          <t>907623</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>927445</t>
+          <t>927273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>983705</t>
+          <t>984845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1009257</t>
+          <t>1009697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1901620</t>
+          <t>1901136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1932954</t>
+          <t>1931870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70617</t>
+          <t>70576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108614</t>
+          <t>106821</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101921</t>
+          <t>101559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142388</t>
+          <t>142806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178837</t>
+          <t>181139</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>234861</t>
+          <t>237608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3166911</t>
+          <t>3168704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3204908</t>
+          <t>3204949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3236809</t>
+          <t>3236391</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3277276</t>
+          <t>3277638</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6419861</t>
+          <t>6417114</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6475885</t>
+          <t>6473583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21694</t>
+          <t>21176</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45398</t>
+          <t>46202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>22870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45218</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48455</t>
+          <t>48220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82041</t>
+          <t>81312</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>652002</t>
+          <t>651198</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>675706</t>
+          <t>676224</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649070</t>
+          <t>648070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>672451</t>
+          <t>671418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1309647</t>
+          <t>1310376</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343233</t>
+          <t>1343468</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27684</t>
+          <t>28459</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54387</t>
+          <t>53464</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40269</t>
+          <t>39849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71117</t>
+          <t>72536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74857</t>
+          <t>74202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112844</t>
+          <t>113808</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>963560</t>
+          <t>964483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>990263</t>
+          <t>989488</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>956658</t>
+          <t>955239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>987506</t>
+          <t>987926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1932879</t>
+          <t>1931915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1970866</t>
+          <t>1971521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39204</t>
+          <t>40923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>25812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50979</t>
+          <t>51609</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>50165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83627</t>
+          <t>84089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717334</t>
+          <t>715615</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>738272</t>
+          <t>737911</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>725304</t>
+          <t>724674</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>749174</t>
+          <t>750471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1449194</t>
+          <t>1448732</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1481632</t>
+          <t>1482656</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29165</t>
+          <t>28903</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59401</t>
+          <t>59997</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50454</t>
+          <t>51181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83194</t>
+          <t>84581</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88744</t>
+          <t>87284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133185</t>
+          <t>128340</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>884538</t>
+          <t>883942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>914774</t>
+          <t>915036</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>965569</t>
+          <t>964182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>998309</t>
+          <t>997582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1859518</t>
+          <t>1864363</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1903959</t>
+          <t>1905419</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114170</t>
+          <t>117282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>166447</t>
+          <t>167490</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163853</t>
+          <t>162886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220822</t>
+          <t>219087</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>295469</t>
+          <t>296390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>369878</t>
+          <t>368209</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3249378</t>
+          <t>3248335</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3301655</t>
+          <t>3298543</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3326288</t>
+          <t>3328023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3383257</t>
+          <t>3384224</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6593056</t>
+          <t>6594725</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6667465</t>
+          <t>6666544</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16095</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37075</t>
+          <t>35803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>22100</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43777</t>
+          <t>44469</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44300</t>
+          <t>43379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72833</t>
+          <t>72877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>637725</t>
+          <t>638997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>658705</t>
+          <t>658590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>629062</t>
+          <t>628370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>651114</t>
+          <t>650739</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1274806</t>
+          <t>1274762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1303339</t>
+          <t>1304260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41310</t>
+          <t>41973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>50707</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49022</t>
+          <t>49894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82104</t>
+          <t>84539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>981121</t>
+          <t>980458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1003559</t>
+          <t>1002514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>992565</t>
+          <t>992206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1018203</t>
+          <t>1017540</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1983240</t>
+          <t>1980805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2016322</t>
+          <t>2015450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34197</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45091</t>
+          <t>45396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40388</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70891</t>
+          <t>71516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>725355</t>
+          <t>725246</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>746193</t>
+          <t>745441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>739920</t>
+          <t>739615</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>764267</t>
+          <t>763857</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1473672</t>
+          <t>1473047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1504175</t>
+          <t>1504819</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>15268</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37132</t>
+          <t>35177</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61973</t>
+          <t>59579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52954</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86711</t>
+          <t>88460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>900435</t>
+          <t>902390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>921840</t>
+          <t>922299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>981806</t>
+          <t>984200</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1011327</t>
+          <t>1011565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1894635</t>
+          <t>1892886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1928392</t>
+          <t>1927972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81052</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122688</t>
+          <t>121868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119777</t>
+          <t>121848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>171144</t>
+          <t>171702</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>213981</t>
+          <t>211384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276229</t>
+          <t>277284</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3271662</t>
+          <t>3272482</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3313298</t>
+          <t>3314228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3373398</t>
+          <t>3372840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3424765</t>
+          <t>3422694</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6662663</t>
+          <t>6661608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6724911</t>
+          <t>6727508</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49307</t>
+          <t>48696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82084</t>
+          <t>82210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74364</t>
+          <t>73858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95256</t>
+          <t>96621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130615</t>
+          <t>128946</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169908</t>
+          <t>168166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>553357</t>
+          <t>553231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>586134</t>
+          <t>586745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>580496</t>
+          <t>579131</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>601388</t>
+          <t>601894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1141286</t>
+          <t>1143028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1180579</t>
+          <t>1182248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>21137</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67213</t>
+          <t>65850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72912</t>
+          <t>73252</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97866</t>
+          <t>97932</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89429</t>
+          <t>91041</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>158823</t>
+          <t>159575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1125651</t>
+          <t>1127014</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1167610</t>
+          <t>1171727</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>860240</t>
+          <t>860174</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>885194</t>
+          <t>884854</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1992148</t>
+          <t>1991396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2061542</t>
+          <t>2059930</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25378</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45961</t>
+          <t>47430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54170</t>
+          <t>53754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47118</t>
+          <t>46920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92190</t>
+          <t>90963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>657723</t>
+          <t>656254</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678306</t>
+          <t>677844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>878630</t>
+          <t>879046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>912114</t>
+          <t>914690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1544294</t>
+          <t>1545521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1589366</t>
+          <t>1589564</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49534</t>
+          <t>49649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77556</t>
+          <t>75546</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61300</t>
+          <t>63264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93474</t>
+          <t>93790</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120845</t>
+          <t>120992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162822</t>
+          <t>163212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>849275</t>
+          <t>851285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877297</t>
+          <t>877182</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>997900</t>
+          <t>997584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1030074</t>
+          <t>1028110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1855383</t>
+          <t>1854993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897360</t>
+          <t>1897213</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>164059</t>
+          <t>157256</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>239591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>231207</t>
+          <t>235759</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>317937</t>
+          <t>319722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>430868</t>
+          <t>428459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>543050</t>
+          <t>539202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3217810</t>
+          <t>3219229</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3294761</t>
+          <t>3301564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3340096</t>
+          <t>3338311</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3426826</t>
+          <t>3422274</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6573803</t>
+          <t>6577651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6685985</t>
+          <t>6688394</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A13-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A13-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>13231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31585</t>
+          <t>30342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19295</t>
+          <t>19178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39022</t>
+          <t>39572</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>678147</t>
+          <t>677906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>689072</t>
+          <t>689096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>656766</t>
+          <t>658009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>675270</t>
+          <t>675120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1342323</t>
+          <t>1341773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1362050</t>
+          <t>1362167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20576</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43017</t>
+          <t>41812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20278</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41874</t>
+          <t>41269</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45949</t>
+          <t>45751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77715</t>
+          <t>77774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>918783</t>
+          <t>919988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>941224</t>
+          <t>941262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>926519</t>
+          <t>927124</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>948115</t>
+          <t>947481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1852478</t>
+          <t>1852419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1884244</t>
+          <t>1884442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35952</t>
+          <t>35503</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22412</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43229</t>
+          <t>43945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42969</t>
+          <t>43255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71666</t>
+          <t>71420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642557</t>
+          <t>643006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662659</t>
+          <t>662675</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>640612</t>
+          <t>639896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>661429</t>
+          <t>661923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1290684</t>
+          <t>1290930</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1319381</t>
+          <t>1319095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34599</t>
+          <t>34844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28915</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53767</t>
+          <t>53834</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48964</t>
+          <t>48922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79698</t>
+          <t>81503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>907623</t>
+          <t>907378</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>927273</t>
+          <t>927161</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>984845</t>
+          <t>984778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1009697</t>
+          <t>1008953</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1901136</t>
+          <t>1899331</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1931870</t>
+          <t>1931912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70576</t>
+          <t>70173</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106821</t>
+          <t>105971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101559</t>
+          <t>102113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142806</t>
+          <t>142944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>182237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>237608</t>
+          <t>239500</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3168704</t>
+          <t>3169554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3204949</t>
+          <t>3205352</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3236391</t>
+          <t>3236253</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3277638</t>
+          <t>3277084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6417114</t>
+          <t>6415222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6473583</t>
+          <t>6472485</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21176</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46202</t>
+          <t>48143</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46218</t>
+          <t>45438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48220</t>
+          <t>48630</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81312</t>
+          <t>81878</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>651198</t>
+          <t>649257</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>676224</t>
+          <t>675390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>648070</t>
+          <t>648850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671418</t>
+          <t>672279</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1310376</t>
+          <t>1309810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343468</t>
+          <t>1343058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28459</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53464</t>
+          <t>55186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39849</t>
+          <t>40400</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72536</t>
+          <t>70779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74202</t>
+          <t>74451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113808</t>
+          <t>114181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>964483</t>
+          <t>962761</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>989488</t>
+          <t>990425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>955239</t>
+          <t>956996</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>987926</t>
+          <t>987375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1931915</t>
+          <t>1931542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1971521</t>
+          <t>1971272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40923</t>
+          <t>39839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25812</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51609</t>
+          <t>52857</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50165</t>
+          <t>50615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84089</t>
+          <t>82586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>715615</t>
+          <t>716699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>737911</t>
+          <t>737322</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>724674</t>
+          <t>723426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>750471</t>
+          <t>749826</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1448732</t>
+          <t>1450235</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1482656</t>
+          <t>1482206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28903</t>
+          <t>29904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59997</t>
+          <t>57634</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51181</t>
+          <t>51148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84581</t>
+          <t>82670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87284</t>
+          <t>86163</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128340</t>
+          <t>131708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>883942</t>
+          <t>886305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>915036</t>
+          <t>914035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>964182</t>
+          <t>966093</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>997582</t>
+          <t>997615</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1864363</t>
+          <t>1860995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1905419</t>
+          <t>1906540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117282</t>
+          <t>116213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>167490</t>
+          <t>165627</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162886</t>
+          <t>165743</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219087</t>
+          <t>220736</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>296390</t>
+          <t>294840</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>368209</t>
+          <t>368516</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3248335</t>
+          <t>3250198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3298543</t>
+          <t>3299612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3328023</t>
+          <t>3326374</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3384224</t>
+          <t>3381367</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6594725</t>
+          <t>6594418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6666544</t>
+          <t>6668094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35803</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22100</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44469</t>
+          <t>44896</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43379</t>
+          <t>43536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72877</t>
+          <t>73417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>638997</t>
+          <t>639048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>658590</t>
+          <t>658947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>628370</t>
+          <t>627943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>650739</t>
+          <t>650855</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1274762</t>
+          <t>1274222</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1304260</t>
+          <t>1304103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19917</t>
+          <t>19741</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41973</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>24875</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50707</t>
+          <t>49971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49894</t>
+          <t>49655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84539</t>
+          <t>83620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>980458</t>
+          <t>980470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1002514</t>
+          <t>1002690</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>992206</t>
+          <t>992942</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1017540</t>
+          <t>1018038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1980805</t>
+          <t>1981724</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2015450</t>
+          <t>2015689</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14111</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34306</t>
+          <t>35573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21154</t>
+          <t>21967</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45396</t>
+          <t>45689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>39906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71516</t>
+          <t>72255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>725246</t>
+          <t>723979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>745441</t>
+          <t>745957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>739615</t>
+          <t>739322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>763857</t>
+          <t>763044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1473047</t>
+          <t>1472308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1504819</t>
+          <t>1504657</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15268</t>
+          <t>15097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35177</t>
+          <t>34670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32214</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59579</t>
+          <t>61875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53374</t>
+          <t>53058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88460</t>
+          <t>89555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>902390</t>
+          <t>902897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922299</t>
+          <t>922470</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>984200</t>
+          <t>981904</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1011565</t>
+          <t>1011115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1892886</t>
+          <t>1891791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1927972</t>
+          <t>1928288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>82159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121868</t>
+          <t>123631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121848</t>
+          <t>119203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>171702</t>
+          <t>171138</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211384</t>
+          <t>213192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>277284</t>
+          <t>277135</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3272482</t>
+          <t>3270719</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3314228</t>
+          <t>3312191</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3372840</t>
+          <t>3373404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3422694</t>
+          <t>3425339</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6661608</t>
+          <t>6661757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6727508</t>
+          <t>6725700</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>62083</t>
+          <t>60944</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48696</t>
+          <t>49036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82210</t>
+          <t>77801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>84501</t>
+          <t>89295</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73858</t>
+          <t>77987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96621</t>
+          <t>103104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>146584</t>
+          <t>150239</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>128946</t>
+          <t>133209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168166</t>
+          <t>171848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>573358</t>
+          <t>629766</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>553231</t>
+          <t>612909</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>586745</t>
+          <t>641674</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>591251</t>
+          <t>643818</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>579131</t>
+          <t>630009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>601894</t>
+          <t>655126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1164610</t>
+          <t>1273584</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1143028</t>
+          <t>1251975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1182248</t>
+          <t>1290614</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48443</t>
+          <t>53330</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65850</t>
+          <t>67213</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84810</t>
+          <t>92908</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73252</t>
+          <t>77605</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97932</t>
+          <t>107610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>133253</t>
+          <t>146238</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91041</t>
+          <t>127908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159575</t>
+          <t>167423</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1144421</t>
+          <t>995587</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1127014</t>
+          <t>981704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1171727</t>
+          <t>1007917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>873296</t>
+          <t>977930</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>860174</t>
+          <t>963228</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>884854</t>
+          <t>993233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2017718</t>
+          <t>1973517</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1991396</t>
+          <t>1952332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2059930</t>
+          <t>1991847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34644</t>
+          <t>39199</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25840</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47430</t>
+          <t>52741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38310</t>
+          <t>43483</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18110</t>
+          <t>34119</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53754</t>
+          <t>54420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>72954</t>
+          <t>82681</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46920</t>
+          <t>69155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90963</t>
+          <t>102247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>669040</t>
+          <t>762887</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656254</t>
+          <t>749345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>677844</t>
+          <t>773468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>894490</t>
+          <t>768180</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>879046</t>
+          <t>757243</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>914690</t>
+          <t>777544</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1563530</t>
+          <t>1531067</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1545521</t>
+          <t>1511501</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1589564</t>
+          <t>1544593</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62956</t>
+          <t>66901</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49649</t>
+          <t>53303</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75546</t>
+          <t>81809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>78890</t>
+          <t>87034</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63264</t>
+          <t>74218</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93790</t>
+          <t>101951</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>141845</t>
+          <t>153935</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120992</t>
+          <t>134979</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163212</t>
+          <t>175241</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>863875</t>
+          <t>923161</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>851285</t>
+          <t>908253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877182</t>
+          <t>936759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1012484</t>
+          <t>1029997</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>997584</t>
+          <t>1015080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1028110</t>
+          <t>1042813</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1876360</t>
+          <t>1953158</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1854993</t>
+          <t>1931852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897213</t>
+          <t>1972114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>208125</t>
+          <t>220373</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157256</t>
+          <t>193771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239591</t>
+          <t>249185</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>286511</t>
+          <t>312720</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>235759</t>
+          <t>285399</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>319722</t>
+          <t>338445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>494636</t>
+          <t>533093</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>428459</t>
+          <t>493532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>539202</t>
+          <t>573701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3250695</t>
+          <t>3311402</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3219229</t>
+          <t>3282590</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3301564</t>
+          <t>3338004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3371522</t>
+          <t>3419925</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3338311</t>
+          <t>3394200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3422274</t>
+          <t>3447246</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6622217</t>
+          <t>6731326</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6577651</t>
+          <t>6690718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6688394</t>
+          <t>6770887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
